--- a/Classes/ECE (Daffodil)/FORMAT OF PROFILE DATA.xlsx
+++ b/Classes/ECE (Daffodil)/FORMAT OF PROFILE DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Classes\ECE (Daffodil)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD4C733-4267-4CD3-BD59-0EBFE0BBD204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CDA41B3-FC7B-40AD-BE95-5C40497934DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Record" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="508">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -118,36 +118,18 @@
     <t>Sikandar</t>
   </si>
   <si>
-    <t>Ab. Rehman</t>
-  </si>
-  <si>
     <t>M. Aslam</t>
   </si>
   <si>
     <t>Ahmed Zia</t>
   </si>
   <si>
-    <t>Zia Buksh</t>
-  </si>
-  <si>
-    <t>Arham</t>
-  </si>
-  <si>
-    <t>Qasim Memon</t>
-  </si>
-  <si>
-    <t>Amar Farooque</t>
-  </si>
-  <si>
     <t>M. Farooque</t>
   </si>
   <si>
     <t>Ashfaque</t>
   </si>
   <si>
-    <t>M. Zubair</t>
-  </si>
-  <si>
     <t>Fahad</t>
   </si>
   <si>
@@ -214,9 +196,6 @@
     <t>Shaheer Ahmed</t>
   </si>
   <si>
-    <t>Ahmed Rizwan</t>
-  </si>
-  <si>
     <t>Shahzain</t>
   </si>
   <si>
@@ -271,9 +250,6 @@
     <t>Imtiaz Hussain</t>
   </si>
   <si>
-    <t>Aniza Memon</t>
-  </si>
-  <si>
     <t>M. Qasim</t>
   </si>
   <si>
@@ -295,9 +271,6 @@
     <t>Khalid Hussain</t>
   </si>
   <si>
-    <t>Faiza</t>
-  </si>
-  <si>
     <t>Liaqat Ali</t>
   </si>
   <si>
@@ -316,9 +289,6 @@
     <t>Meeral</t>
   </si>
   <si>
-    <t>Kauser Fatima</t>
-  </si>
-  <si>
     <t>Amir Jamil</t>
   </si>
   <si>
@@ -328,9 +298,6 @@
     <t>Aijaz Ali</t>
   </si>
   <si>
-    <t>Mirha</t>
-  </si>
-  <si>
     <t>M. Luqman</t>
   </si>
   <si>
@@ -343,9 +310,6 @@
     <t>Rimsha</t>
   </si>
   <si>
-    <t>Meer Ameer-ud-Din</t>
-  </si>
-  <si>
     <t>Sidra</t>
   </si>
   <si>
@@ -355,12 +319,6 @@
     <t>M. Khan</t>
   </si>
   <si>
-    <t>Taniya Bibi</t>
-  </si>
-  <si>
-    <t>Wazir Ali</t>
-  </si>
-  <si>
     <t>Tanzeela</t>
   </si>
   <si>
@@ -1201,9 +1159,6 @@
     <t>Abdul Wasay</t>
   </si>
   <si>
-    <t>Muhammad Aslam</t>
-  </si>
-  <si>
     <t>43206-5603425-5</t>
   </si>
   <si>
@@ -1475,6 +1430,132 @@
   </si>
   <si>
     <t>ECE (ROSE)</t>
+  </si>
+  <si>
+    <t>43303-0554359-1</t>
+  </si>
+  <si>
+    <t>M. Akram</t>
+  </si>
+  <si>
+    <t>42501-0179592-5</t>
+  </si>
+  <si>
+    <t>42501-7866370-9</t>
+  </si>
+  <si>
+    <t>Anaiza Memon</t>
+  </si>
+  <si>
+    <t>42501-5037157-9</t>
+  </si>
+  <si>
+    <t>43203-4340920-1</t>
+  </si>
+  <si>
+    <t>43203-2137059-1</t>
+  </si>
+  <si>
+    <t>Kausar Fatima</t>
+  </si>
+  <si>
+    <t>42201-5442330-3</t>
+  </si>
+  <si>
+    <t>45202-0753776-1</t>
+  </si>
+  <si>
+    <t>Mir Amir Udin Mirzada</t>
+  </si>
+  <si>
+    <t>0342-8248146</t>
+  </si>
+  <si>
+    <t>45202-4803252-1</t>
+  </si>
+  <si>
+    <t>45202-8028394-1</t>
+  </si>
+  <si>
+    <t>43205-1141000-5</t>
+  </si>
+  <si>
+    <t>45301-1365928-1</t>
+  </si>
+  <si>
+    <t>42201-5613476-7</t>
+  </si>
+  <si>
+    <t>Minha</t>
+  </si>
+  <si>
+    <t>43304-3062534-5</t>
+  </si>
+  <si>
+    <t>43304-0589629-5</t>
+  </si>
+  <si>
+    <t>41201-9807804-1</t>
+  </si>
+  <si>
+    <t>Tania Bibi</t>
+  </si>
+  <si>
+    <t>Wazeer Ali</t>
+  </si>
+  <si>
+    <t>42501-4449106-7</t>
+  </si>
+  <si>
+    <t>45302-1837246-1</t>
+  </si>
+  <si>
+    <t>41205-6913258-7</t>
+  </si>
+  <si>
+    <t>42501-7320269-9</t>
+  </si>
+  <si>
+    <t>Faiza Jamali</t>
+  </si>
+  <si>
+    <t>42501-7318763-3</t>
+  </si>
+  <si>
+    <t>Ammar Farooque</t>
+  </si>
+  <si>
+    <t>43504-0366567-5</t>
+  </si>
+  <si>
+    <t>43205-9031532-7</t>
+  </si>
+  <si>
+    <t>43301-0123584-7</t>
+  </si>
+  <si>
+    <t>Rizwan Ahmed</t>
+  </si>
+  <si>
+    <t>42301-8541923-5</t>
+  </si>
+  <si>
+    <t>Arham Memon</t>
+  </si>
+  <si>
+    <t>Zubair Ahmed</t>
+  </si>
+  <si>
+    <t>43304-3873615-7</t>
+  </si>
+  <si>
+    <t>45208-9708949-3</t>
+  </si>
+  <si>
+    <t>Khuda Baksh Zia</t>
+  </si>
+  <si>
+    <t>38403-9293384-3</t>
   </si>
 </sst>
 </file>
@@ -1484,12 +1565,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1675,66 +1763,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1987,26 +2086,26 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="22"/>
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstColumn" dxfId="19"/>
-      <tableStyleElement type="lastColumn" dxfId="18"/>
-      <tableStyleElement type="firstRowStripe" dxfId="17"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="totalRow" dxfId="21"/>
+      <tableStyleElement type="firstColumn" dxfId="20"/>
+      <tableStyleElement type="lastColumn" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstRowStripe" dxfId="13"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="12"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="10"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="9"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="8"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="7"/>
-      <tableStyleElement type="pageFieldValues" dxfId="6"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2300,23 +2399,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15" s="20" customFormat="1" ht="15.75">
       <c r="A2" s="2" t="s">
@@ -2338,7 +2437,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="H2" s="23" t="s">
         <v>7</v>
@@ -2366,7 +2465,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A3" s="31">
+      <c r="A3" s="30">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2374,16 +2473,16 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>480</v>
+        <v>391</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H3" s="23"/>
       <c r="I3" s="3"/>
@@ -2395,7 +2494,7 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A4" s="31">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -2403,16 +2502,16 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="8" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>480</v>
+        <v>221</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="3"/>
@@ -2424,7 +2523,7 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A5" s="31">
+      <c r="A5" s="30">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -2432,16 +2531,16 @@
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="8" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>480</v>
+        <v>394</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H5" s="23"/>
       <c r="I5" s="3"/>
@@ -2453,7 +2552,7 @@
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A6" s="31">
+      <c r="A6" s="30">
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
@@ -2463,16 +2562,16 @@
         <v>135</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>480</v>
+        <v>216</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H6" s="23"/>
       <c r="I6" s="3"/>
@@ -2484,7 +2583,7 @@
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A7" s="31">
+      <c r="A7" s="30">
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -2494,16 +2593,16 @@
         <v>136</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>480</v>
+        <v>396</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H7" s="23"/>
       <c r="I7" s="3"/>
@@ -2515,7 +2614,7 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A8" s="31">
+      <c r="A8" s="30">
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
@@ -2525,16 +2624,16 @@
         <v>137</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>480</v>
+        <v>398</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H8" s="23"/>
       <c r="I8" s="3"/>
@@ -2546,7 +2645,7 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A9" s="31">
+      <c r="A9" s="30">
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -2556,16 +2655,16 @@
         <v>139</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>480</v>
+        <v>400</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="3"/>
@@ -2577,7 +2676,7 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A10" s="31">
+      <c r="A10" s="30">
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
@@ -2585,16 +2684,16 @@
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="8" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>480</v>
+        <v>152</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H10" s="23"/>
       <c r="I10" s="3"/>
@@ -2606,7 +2705,7 @@
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A11" s="31">
+      <c r="A11" s="30">
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -2616,16 +2715,16 @@
         <v>142</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>480</v>
+        <v>403</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H11" s="23"/>
       <c r="I11" s="3"/>
@@ -2637,7 +2736,7 @@
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A12" s="31">
+      <c r="A12" s="30">
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
@@ -2647,16 +2746,16 @@
         <v>143</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>480</v>
+        <v>87</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="3"/>
@@ -2668,7 +2767,7 @@
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A13" s="31">
+      <c r="A13" s="30">
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
@@ -2678,16 +2777,16 @@
         <v>144</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>480</v>
+        <v>406</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H13" s="23"/>
       <c r="I13" s="3"/>
@@ -2699,7 +2798,7 @@
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A14" s="31">
+      <c r="A14" s="30">
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
@@ -2709,16 +2808,16 @@
         <v>145</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>480</v>
+        <v>407</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H14" s="23"/>
       <c r="I14" s="3"/>
@@ -2730,7 +2829,7 @@
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A15" s="31">
+      <c r="A15" s="30">
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
@@ -2740,16 +2839,16 @@
         <v>146</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>480</v>
+        <v>409</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H15" s="23"/>
       <c r="I15" s="3"/>
@@ -2761,7 +2860,7 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A16" s="31">
+      <c r="A16" s="30">
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
@@ -2771,16 +2870,16 @@
         <v>148</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>480</v>
+        <v>411</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="3"/>
@@ -2792,7 +2891,7 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A17" s="31">
+      <c r="A17" s="30">
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
@@ -2802,16 +2901,16 @@
         <v>150</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>480</v>
+        <v>413</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H17" s="23"/>
       <c r="I17" s="3"/>
@@ -2823,7 +2922,7 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A18" s="31">
+      <c r="A18" s="30">
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
@@ -2833,16 +2932,16 @@
         <v>151</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>480</v>
+        <v>415</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H18" s="23"/>
       <c r="I18" s="3"/>
@@ -2854,7 +2953,7 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A19" s="31">
+      <c r="A19" s="30">
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
@@ -2864,16 +2963,16 @@
         <v>152</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>480</v>
+        <v>417</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H19" s="23"/>
       <c r="I19" s="3"/>
@@ -2885,7 +2984,7 @@
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A20" s="31">
+      <c r="A20" s="30">
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
@@ -2895,16 +2994,16 @@
         <v>153</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>480</v>
+        <v>419</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H20" s="23"/>
       <c r="I20" s="3"/>
@@ -2916,7 +3015,7 @@
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A21" s="31">
+      <c r="A21" s="30">
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
@@ -2926,16 +3025,16 @@
         <v>154</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>480</v>
+        <v>291</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H21" s="23"/>
       <c r="I21" s="3"/>
@@ -2947,7 +3046,7 @@
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A22" s="31">
+      <c r="A22" s="30">
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
@@ -2957,16 +3056,16 @@
         <v>155</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" s="31" t="s">
-        <v>480</v>
+        <v>49</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H22" s="23"/>
       <c r="I22" s="3"/>
@@ -2978,7 +3077,7 @@
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A23" s="31">
+      <c r="A23" s="30">
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -2988,16 +3087,16 @@
         <v>156</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>480</v>
+        <v>256</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23" s="3"/>
@@ -3009,7 +3108,7 @@
       <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A24" s="31">
+      <c r="A24" s="30">
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
@@ -3019,16 +3118,16 @@
         <v>158</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" s="31" t="s">
-        <v>480</v>
+        <v>252</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H24" s="23"/>
       <c r="I24" s="3"/>
@@ -3040,7 +3139,7 @@
       <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A25" s="31">
+      <c r="A25" s="30">
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
@@ -3050,16 +3149,16 @@
         <v>159</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="F25" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="31" t="s">
-        <v>480</v>
+        <v>425</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="3"/>
@@ -3071,7 +3170,7 @@
       <c r="O25" s="2"/>
     </row>
     <row r="26" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A26" s="31">
+      <c r="A26" s="30">
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
@@ -3081,16 +3180,16 @@
         <v>160</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G26" s="31" t="s">
-        <v>480</v>
+        <v>302</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H26" s="23"/>
       <c r="I26" s="3"/>
@@ -3102,7 +3201,7 @@
       <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A27" s="31">
+      <c r="A27" s="30">
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -3112,16 +3211,16 @@
         <v>161</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>480</v>
+        <v>428</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H27" s="23"/>
       <c r="I27" s="3"/>
@@ -3133,7 +3232,7 @@
       <c r="O27" s="2"/>
     </row>
     <row r="28" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A28" s="31">
+      <c r="A28" s="30">
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
@@ -3143,16 +3242,16 @@
         <v>162</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="F28" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>480</v>
+        <v>430</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H28" s="23"/>
       <c r="I28" s="3"/>
@@ -3164,7 +3263,7 @@
       <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A29" s="31">
+      <c r="A29" s="30">
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
@@ -3174,16 +3273,16 @@
         <v>163</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>480</v>
+        <v>432</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H29" s="23"/>
       <c r="I29" s="3"/>
@@ -3195,7 +3294,7 @@
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A30" s="31">
+      <c r="A30" s="30">
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
@@ -3205,16 +3304,16 @@
         <v>165</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>480</v>
+        <v>434</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H30" s="23"/>
       <c r="I30" s="3"/>
@@ -3226,7 +3325,7 @@
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A31" s="31">
+      <c r="A31" s="30">
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
@@ -3236,16 +3335,16 @@
         <v>166</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="F31" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>480</v>
+        <v>436</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H31" s="23"/>
       <c r="I31" s="3"/>
@@ -3257,7 +3356,7 @@
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A32" s="31">
+      <c r="A32" s="30">
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
@@ -3267,16 +3366,16 @@
         <v>167</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="F32" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="31" t="s">
-        <v>480</v>
+        <v>436</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H32" s="23"/>
       <c r="I32" s="3"/>
@@ -3288,7 +3387,7 @@
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A33" s="31">
+      <c r="A33" s="30">
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
@@ -3298,16 +3397,16 @@
         <v>168</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G33" s="31" t="s">
-        <v>480</v>
+        <v>55</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H33" s="23"/>
       <c r="I33" s="3"/>
@@ -3319,7 +3418,7 @@
       <c r="O33" s="2"/>
     </row>
     <row r="34" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A34" s="31">
+      <c r="A34" s="30">
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
@@ -3329,16 +3428,16 @@
         <v>169</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="F34" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G34" s="31" t="s">
-        <v>480</v>
+        <v>440</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G34" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H34" s="23"/>
       <c r="I34" s="3"/>
@@ -3350,7 +3449,7 @@
       <c r="O34" s="2"/>
     </row>
     <row r="35" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A35" s="31">
+      <c r="A35" s="30">
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
@@ -3360,16 +3459,16 @@
         <v>170</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="F35" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G35" s="31" t="s">
-        <v>480</v>
+        <v>442</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H35" s="23"/>
       <c r="I35" s="3"/>
@@ -3381,7 +3480,7 @@
       <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A36" s="31">
+      <c r="A36" s="30">
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -3391,16 +3490,16 @@
         <v>171</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F36" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G36" s="31" t="s">
-        <v>480</v>
+        <v>304</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G36" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H36" s="23"/>
       <c r="I36" s="3"/>
@@ -3412,7 +3511,7 @@
       <c r="O36" s="2"/>
     </row>
     <row r="37" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A37" s="31">
+      <c r="A37" s="30">
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
@@ -3422,16 +3521,16 @@
         <v>172</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="F37" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G37" s="31" t="s">
-        <v>480</v>
+        <v>445</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H37" s="23"/>
       <c r="I37" s="3"/>
@@ -3443,7 +3542,7 @@
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A38" s="31">
+      <c r="A38" s="30">
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
@@ -3453,16 +3552,16 @@
         <v>196</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="F38" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G38" s="31" t="s">
-        <v>480</v>
+        <v>174</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H38" s="23"/>
       <c r="I38" s="3"/>
@@ -3474,7 +3573,7 @@
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A39" s="31">
+      <c r="A39" s="30">
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
@@ -3484,14 +3583,14 @@
         <v>197</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="E39" s="9"/>
-      <c r="F39" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>480</v>
+      <c r="F39" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H39" s="23"/>
       <c r="I39" s="3"/>
@@ -3503,7 +3602,7 @@
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A40" s="31">
+      <c r="A40" s="30">
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
@@ -3513,16 +3612,16 @@
         <v>180</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="F40" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G40" s="31" t="s">
-        <v>480</v>
+        <v>448</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H40" s="23"/>
       <c r="I40" s="3"/>
@@ -3534,7 +3633,7 @@
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A41" s="31">
+      <c r="A41" s="30">
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
@@ -3544,16 +3643,16 @@
         <v>182</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G41" s="30" t="s">
         <v>465</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G41" s="31" t="s">
-        <v>480</v>
       </c>
       <c r="H41" s="23"/>
       <c r="I41" s="3"/>
@@ -3565,7 +3664,7 @@
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A42" s="31">
+      <c r="A42" s="30">
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
@@ -3575,16 +3674,16 @@
         <v>186</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F42" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G42" s="31" t="s">
-        <v>480</v>
+        <v>117</v>
+      </c>
+      <c r="F42" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H42" s="23"/>
       <c r="I42" s="3"/>
@@ -3596,7 +3695,7 @@
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A43" s="31">
+      <c r="A43" s="30">
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
@@ -3606,16 +3705,16 @@
         <v>188</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>480</v>
+        <v>452</v>
+      </c>
+      <c r="F43" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H43" s="23"/>
       <c r="I43" s="3"/>
@@ -3627,7 +3726,7 @@
       <c r="O43" s="2"/>
     </row>
     <row r="44" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A44" s="31">
+      <c r="A44" s="30">
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
@@ -3637,16 +3736,16 @@
         <v>191</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="F44" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G44" s="31" t="s">
-        <v>480</v>
+        <v>454</v>
+      </c>
+      <c r="F44" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H44" s="23"/>
       <c r="I44" s="3"/>
@@ -3658,7 +3757,7 @@
       <c r="O44" s="2"/>
     </row>
     <row r="45" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A45" s="31">
+      <c r="A45" s="30">
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
@@ -3666,16 +3765,16 @@
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="8" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F45" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G45" s="31" t="s">
-        <v>480</v>
+        <v>64</v>
+      </c>
+      <c r="F45" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H45" s="23"/>
       <c r="I45" s="3"/>
@@ -3687,7 +3786,7 @@
       <c r="O45" s="2"/>
     </row>
     <row r="46" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A46" s="31">
+      <c r="A46" s="30">
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
@@ -3697,16 +3796,16 @@
         <v>195</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="F46" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G46" s="31" t="s">
-        <v>480</v>
+        <v>253</v>
+      </c>
+      <c r="F46" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G46" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H46" s="23"/>
       <c r="I46" s="3"/>
@@ -3718,7 +3817,7 @@
       <c r="O46" s="2"/>
     </row>
     <row r="47" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A47" s="31">
+      <c r="A47" s="30">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
@@ -3726,16 +3825,16 @@
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="8" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>480</v>
+        <v>458</v>
+      </c>
+      <c r="F47" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G47" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H47" s="23"/>
       <c r="I47" s="3"/>
@@ -3747,24 +3846,24 @@
       <c r="O47" s="2"/>
     </row>
     <row r="48" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A48" s="31">
+      <c r="A48" s="30">
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="27"/>
-      <c r="D48" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="F48" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>480</v>
+      <c r="C48" s="26"/>
+      <c r="D48" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="F48" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H48" s="23"/>
       <c r="I48" s="3"/>
@@ -3776,24 +3875,24 @@
       <c r="O48" s="2"/>
     </row>
     <row r="49" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A49" s="31">
+      <c r="A49" s="30">
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30" t="s">
-        <v>476</v>
-      </c>
-      <c r="E49" s="30" t="s">
-        <v>410</v>
-      </c>
-      <c r="F49" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G49" s="31" t="s">
-        <v>480</v>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>395</v>
+      </c>
+      <c r="F49" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G49" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H49" s="23"/>
       <c r="I49" s="3"/>
@@ -3805,24 +3904,24 @@
       <c r="O49" s="2"/>
     </row>
     <row r="50" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A50" s="31">
+      <c r="A50" s="30">
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30" t="s">
-        <v>477</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>478</v>
-      </c>
-      <c r="F50" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G50" s="31" t="s">
-        <v>480</v>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="F50" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H50" s="23"/>
       <c r="I50" s="3"/>
@@ -3834,24 +3933,24 @@
       <c r="O50" s="2"/>
     </row>
     <row r="51" spans="1:15" s="20" customFormat="1" ht="15.75">
-      <c r="A51" s="31">
+      <c r="A51" s="30">
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="E51" s="30" t="s">
-        <v>479</v>
-      </c>
-      <c r="F51" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G51" s="31" t="s">
-        <v>480</v>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>464</v>
+      </c>
+      <c r="F51" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G51" s="30" t="s">
+        <v>465</v>
       </c>
       <c r="H51" s="23"/>
       <c r="I51" s="3"/>
@@ -3878,11 +3977,11 @@
       <c r="E52" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F52" s="31" t="s">
-        <v>74</v>
+      <c r="F52" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H52" s="22">
         <v>44251</v>
@@ -3895,7 +3994,7 @@
       </c>
       <c r="K52" s="22"/>
       <c r="L52" s="10" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10"/>
@@ -3919,11 +4018,11 @@
       <c r="E53" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F53" s="31" t="s">
-        <v>74</v>
+      <c r="F53" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H53" s="22"/>
       <c r="I53" s="14" t="s">
@@ -3954,11 +4053,11 @@
       <c r="E54" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="31" t="s">
-        <v>74</v>
+      <c r="F54" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H54" s="22"/>
       <c r="I54" s="14" t="s">
@@ -3989,11 +4088,11 @@
       <c r="E55" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F55" s="31" t="s">
-        <v>74</v>
+      <c r="F55" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H55" s="22"/>
       <c r="I55" s="14" t="s">
@@ -4024,11 +4123,11 @@
       <c r="E56" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F56" s="31" t="s">
-        <v>74</v>
+      <c r="F56" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H56" s="22"/>
       <c r="I56" s="14" t="s">
@@ -4054,29 +4153,37 @@
         <v>95</v>
       </c>
       <c r="D57" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E57" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E57" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F57" s="31" t="s">
-        <v>74</v>
+      <c r="F57" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H57" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H57" s="22">
+        <v>42464</v>
+      </c>
       <c r="I57" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J57" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K57" s="22"/>
-      <c r="L57" s="10"/>
+      <c r="K57" s="22">
+        <v>45143</v>
+      </c>
+      <c r="L57" s="31" t="s">
+        <v>375</v>
+      </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
+      <c r="O57" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="10">
@@ -4089,26 +4196,32 @@
         <v>96</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F58" s="31" t="s">
-        <v>74</v>
+        <v>506</v>
+      </c>
+      <c r="F58" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H58" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H58" s="22">
+        <v>43593</v>
+      </c>
       <c r="I58" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J58" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K58" s="22"/>
-      <c r="L58" s="10"/>
+      <c r="K58" s="22">
+        <v>45143</v>
+      </c>
+      <c r="L58" s="31" t="s">
+        <v>507</v>
+      </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
       <c r="O58" s="10"/>
@@ -4124,29 +4237,37 @@
         <v>108</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>32</v>
+        <v>502</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F59" s="31" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="F59" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H59" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H59" s="22">
+        <v>44174</v>
+      </c>
       <c r="I59" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J59" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K59" s="22"/>
-      <c r="L59" s="10"/>
+      <c r="K59" s="22">
+        <v>45173</v>
+      </c>
+      <c r="L59" s="31" t="s">
+        <v>471</v>
+      </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
+      <c r="O59" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="10">
@@ -4159,16 +4280,16 @@
         <v>131</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>34</v>
+        <v>496</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F60" s="31" t="s">
-        <v>74</v>
+        <v>30</v>
+      </c>
+      <c r="F60" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H60" s="22">
         <v>43607</v>
@@ -4182,7 +4303,9 @@
       <c r="K60" s="22">
         <v>45231</v>
       </c>
-      <c r="L60" s="10"/>
+      <c r="L60" s="31" t="s">
+        <v>497</v>
+      </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
       <c r="O60" s="10"/>
@@ -4198,26 +4321,32 @@
         <v>101</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F61" s="31" t="s">
-        <v>74</v>
+        <v>503</v>
+      </c>
+      <c r="F61" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H61" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H61" s="22">
+        <v>43714</v>
+      </c>
       <c r="I61" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J61" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K61" s="22"/>
-      <c r="L61" s="10"/>
+      <c r="K61" s="22">
+        <v>45145</v>
+      </c>
+      <c r="L61" s="31" t="s">
+        <v>504</v>
+      </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
       <c r="O61" s="10"/>
@@ -4233,16 +4362,16 @@
         <v>100</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F62" s="31" t="s">
-        <v>74</v>
+        <v>33</v>
+      </c>
+      <c r="F62" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H62" s="22"/>
       <c r="I62" s="14" t="s">
@@ -4268,16 +4397,16 @@
         <v>90</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F63" s="31" t="s">
-        <v>74</v>
+        <v>35</v>
+      </c>
+      <c r="F63" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H63" s="22"/>
       <c r="I63" s="14" t="s">
@@ -4303,16 +4432,16 @@
         <v>73</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F64" s="31" t="s">
-        <v>74</v>
+        <v>37</v>
+      </c>
+      <c r="F64" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H64" s="22"/>
       <c r="I64" s="14" t="s">
@@ -4338,16 +4467,16 @@
         <v>72</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F65" s="31" t="s">
-        <v>74</v>
+        <v>39</v>
+      </c>
+      <c r="F65" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H65" s="22"/>
       <c r="I65" s="14" t="s">
@@ -4373,16 +4502,16 @@
         <v>74</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F66" s="31" t="s">
-        <v>74</v>
+        <v>41</v>
+      </c>
+      <c r="F66" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H66" s="22"/>
       <c r="I66" s="14" t="s">
@@ -4408,16 +4537,16 @@
         <v>77</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F67" s="31" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="F67" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H67" s="22"/>
       <c r="I67" s="14" t="s">
@@ -4443,16 +4572,16 @@
         <v>80</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F68" s="31" t="s">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="F68" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H68" s="22"/>
       <c r="I68" s="14" t="s">
@@ -4478,16 +4607,16 @@
         <v>92</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F69" s="31" t="s">
-        <v>74</v>
+        <v>47</v>
+      </c>
+      <c r="F69" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H69" s="22"/>
       <c r="I69" s="14" t="s">
@@ -4513,16 +4642,16 @@
         <v>93</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F70" s="31" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="F70" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H70" s="22"/>
       <c r="I70" s="14" t="s">
@@ -4548,16 +4677,16 @@
         <v>14</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F71" s="31" t="s">
-        <v>74</v>
+        <v>51</v>
+      </c>
+      <c r="F71" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H71" s="22"/>
       <c r="I71" s="14" t="s">
@@ -4583,16 +4712,16 @@
         <v>94</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F72" s="31" t="s">
-        <v>74</v>
+        <v>51</v>
+      </c>
+      <c r="F72" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H72" s="22"/>
       <c r="I72" s="14" t="s">
@@ -4618,16 +4747,16 @@
         <v>111</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F73" s="31" t="s">
-        <v>74</v>
+        <v>500</v>
+      </c>
+      <c r="F73" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H73" s="22">
         <v>43789</v>
@@ -4641,7 +4770,9 @@
       <c r="K73" s="22">
         <v>45174</v>
       </c>
-      <c r="L73" s="10"/>
+      <c r="L73" s="31" t="s">
+        <v>501</v>
+      </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10"/>
       <c r="O73" s="10"/>
@@ -4657,16 +4788,16 @@
         <v>113</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F74" s="31" t="s">
-        <v>74</v>
+        <v>55</v>
+      </c>
+      <c r="F74" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H74" s="22">
         <v>43016</v>
@@ -4680,7 +4811,9 @@
       <c r="K74" s="22">
         <v>45180</v>
       </c>
-      <c r="L74" s="10"/>
+      <c r="L74" s="31" t="s">
+        <v>499</v>
+      </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10"/>
       <c r="O74" s="10"/>
@@ -4696,16 +4829,16 @@
         <v>115</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="F75" s="31" t="s">
-        <v>74</v>
+        <v>386</v>
+      </c>
+      <c r="F75" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H75" s="22">
         <v>43490</v>
@@ -4719,7 +4852,9 @@
       <c r="K75" s="22">
         <v>45180</v>
       </c>
-      <c r="L75" s="10"/>
+      <c r="L75" s="31" t="s">
+        <v>498</v>
+      </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10"/>
       <c r="O75" s="10"/>
@@ -4735,16 +4870,16 @@
         <v>114</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="F76" s="31" t="s">
-        <v>74</v>
+        <v>386</v>
+      </c>
+      <c r="F76" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H76" s="22">
         <v>43230</v>
@@ -4774,16 +4909,16 @@
         <v>141</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="F77" s="31" t="s">
-        <v>74</v>
+        <v>59</v>
+      </c>
+      <c r="F77" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H77" s="22"/>
       <c r="I77" s="14" t="s">
@@ -4809,16 +4944,16 @@
         <v>140</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="F78" s="31" t="s">
-        <v>74</v>
+        <v>59</v>
+      </c>
+      <c r="F78" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H78" s="22"/>
       <c r="I78" s="14" t="s">
@@ -4842,14 +4977,14 @@
       </c>
       <c r="C79" s="14"/>
       <c r="D79" s="15" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E79" s="16"/>
-      <c r="F79" s="31" t="s">
-        <v>74</v>
+      <c r="F79" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H79" s="22"/>
       <c r="I79" s="14" t="s">
@@ -4873,24 +5008,32 @@
       </c>
       <c r="C80" s="14"/>
       <c r="D80" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E80" s="16"/>
-      <c r="F80" s="31" t="s">
-        <v>74</v>
+        <v>62</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="F80" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H80" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H80" s="22">
+        <v>44019</v>
+      </c>
       <c r="I80" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J80" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K80" s="22"/>
-      <c r="L80" s="10"/>
+      <c r="K80" s="22">
+        <v>45537</v>
+      </c>
+      <c r="L80" s="31" t="s">
+        <v>468</v>
+      </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10"/>
       <c r="O80" s="10"/>
@@ -4904,16 +5047,16 @@
       </c>
       <c r="C81" s="14"/>
       <c r="D81" s="15" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F81" s="31" t="s">
-        <v>74</v>
+        <v>64</v>
+      </c>
+      <c r="F81" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H81" s="22"/>
       <c r="I81" s="14" t="s">
@@ -4937,24 +5080,32 @@
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E82" s="16"/>
+        <v>65</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>298</v>
+      </c>
       <c r="F82" s="31" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H82" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H82" s="22">
+        <v>43345</v>
+      </c>
       <c r="I82" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J82" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K82" s="22"/>
-      <c r="L82" s="10"/>
+      <c r="K82" s="22">
+        <v>45537</v>
+      </c>
+      <c r="L82" s="31" t="s">
+        <v>466</v>
+      </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10"/>
       <c r="O82" s="10"/>
@@ -4968,14 +5119,14 @@
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="15" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E83" s="16"/>
-      <c r="F83" s="31" t="s">
-        <v>74</v>
+      <c r="F83" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H83" s="22"/>
       <c r="I83" s="14" t="s">
@@ -5001,26 +5152,32 @@
         <v>106</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F84" s="31" t="s">
-        <v>120</v>
+        <v>69</v>
+      </c>
+      <c r="F84" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H84" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H84" s="22">
+        <v>43180</v>
+      </c>
       <c r="I84" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J84" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K84" s="22"/>
-      <c r="L84" s="10"/>
+      <c r="K84" s="22">
+        <v>45166</v>
+      </c>
+      <c r="L84" s="31" t="s">
+        <v>473</v>
+      </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10"/>
       <c r="O84" s="10"/>
@@ -5036,29 +5193,39 @@
         <v>75</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F85" s="31" t="s">
-        <v>120</v>
+        <v>71</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H85" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H85" s="22">
+        <v>44000</v>
+      </c>
       <c r="I85" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J85" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K85" s="22"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
+      <c r="K85" s="22">
+        <v>45139</v>
+      </c>
+      <c r="L85" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>378</v>
+      </c>
       <c r="N85" s="10"/>
-      <c r="O85" s="10"/>
+      <c r="O85" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="86" spans="1:15">
       <c r="A86" s="10">
@@ -5071,29 +5238,37 @@
         <v>109</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>79</v>
+        <v>470</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F86" s="31" t="s">
-        <v>120</v>
+        <v>72</v>
+      </c>
+      <c r="F86" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H86" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H86" s="22">
+        <v>44174</v>
+      </c>
       <c r="I86" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J86" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K86" s="22"/>
-      <c r="L86" s="10"/>
+      <c r="K86" s="22">
+        <v>45173</v>
+      </c>
+      <c r="L86" s="31" t="s">
+        <v>471</v>
+      </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
-      <c r="O86" s="10"/>
+      <c r="O86" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="87" spans="1:15">
       <c r="A87" s="10">
@@ -5106,16 +5281,16 @@
         <v>49</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F87" s="31" t="s">
-        <v>120</v>
+        <v>74</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H87" s="22"/>
       <c r="I87" s="14" t="s">
@@ -5141,29 +5316,37 @@
         <v>104</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F88" s="31" t="s">
-        <v>120</v>
+        <v>76</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H88" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H88" s="22">
+        <v>43452</v>
+      </c>
       <c r="I88" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J88" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K88" s="22"/>
-      <c r="L88" s="10"/>
+      <c r="K88" s="22">
+        <v>45145</v>
+      </c>
+      <c r="L88" s="31" t="s">
+        <v>476</v>
+      </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10"/>
-      <c r="O88" s="10"/>
+      <c r="O88" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="89" spans="1:15">
       <c r="A89" s="10">
@@ -5176,29 +5359,37 @@
         <v>88</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="F89" s="31" t="s">
-        <v>120</v>
+        <v>78</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H89" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H89" s="22">
+        <v>43650</v>
+      </c>
       <c r="I89" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J89" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="22"/>
-      <c r="L89" s="10"/>
+      <c r="K89" s="22">
+        <v>45140</v>
+      </c>
+      <c r="L89" s="31" t="s">
+        <v>480</v>
+      </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10"/>
-      <c r="O89" s="10"/>
+      <c r="O89" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="10">
@@ -5211,26 +5402,32 @@
         <v>59</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>87</v>
+        <v>494</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F90" s="31" t="s">
-        <v>120</v>
+        <v>79</v>
+      </c>
+      <c r="F90" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H90" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H90" s="22">
+        <v>43384</v>
+      </c>
       <c r="I90" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J90" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K90" s="22"/>
-      <c r="L90" s="10"/>
+      <c r="K90" s="22">
+        <v>44775</v>
+      </c>
+      <c r="L90" s="31" t="s">
+        <v>495</v>
+      </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10"/>
       <c r="O90" s="10"/>
@@ -5246,26 +5443,32 @@
         <v>83</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F91" s="31" t="s">
-        <v>120</v>
+        <v>81</v>
+      </c>
+      <c r="F91" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H91" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H91" s="22">
+        <v>43556</v>
+      </c>
       <c r="I91" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J91" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K91" s="22"/>
-      <c r="L91" s="10"/>
+      <c r="K91" s="22">
+        <v>45140</v>
+      </c>
+      <c r="L91" s="31" t="s">
+        <v>486</v>
+      </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10"/>
       <c r="O91" s="10"/>
@@ -5281,29 +5484,37 @@
         <v>89</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F92" s="31" t="s">
-        <v>120</v>
+        <v>35</v>
+      </c>
+      <c r="F92" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H92" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H92" s="22">
+        <v>43593</v>
+      </c>
       <c r="I92" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J92" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K92" s="22"/>
-      <c r="L92" s="10"/>
+      <c r="K92" s="22">
+        <v>45140</v>
+      </c>
+      <c r="L92" s="31" t="s">
+        <v>479</v>
+      </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10"/>
-      <c r="O92" s="10"/>
+      <c r="O92" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="93" spans="1:15">
       <c r="A93" s="10">
@@ -5316,26 +5527,32 @@
         <v>86</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F93" s="31" t="s">
-        <v>120</v>
+        <v>84</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H93" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H93" s="22">
+        <v>43691</v>
+      </c>
       <c r="I93" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J93" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K93" s="22"/>
-      <c r="L93" s="10"/>
+      <c r="K93" s="22">
+        <v>45140</v>
+      </c>
+      <c r="L93" s="31" t="s">
+        <v>482</v>
+      </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10"/>
       <c r="O93" s="10"/>
@@ -5351,26 +5568,32 @@
         <v>105</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>94</v>
+        <v>474</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F94" s="31" t="s">
-        <v>120</v>
+        <v>85</v>
+      </c>
+      <c r="F94" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H94" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H94" s="22">
+        <v>43790</v>
+      </c>
       <c r="I94" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J94" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="22"/>
-      <c r="L94" s="10"/>
+      <c r="K94" s="22">
+        <v>45166</v>
+      </c>
+      <c r="L94" s="31" t="s">
+        <v>475</v>
+      </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10"/>
       <c r="O94" s="10"/>
@@ -5386,26 +5609,32 @@
         <v>107</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="F95" s="31" t="s">
-        <v>120</v>
+        <v>87</v>
+      </c>
+      <c r="F95" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H95" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H95" s="22">
+        <v>43511</v>
+      </c>
       <c r="I95" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J95" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K95" s="22"/>
-      <c r="L95" s="10"/>
+      <c r="K95" s="22">
+        <v>45167</v>
+      </c>
+      <c r="L95" s="31" t="s">
+        <v>472</v>
+      </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10"/>
       <c r="O95" s="10"/>
@@ -5421,26 +5650,32 @@
         <v>84</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>98</v>
+        <v>484</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F96" s="31" t="s">
-        <v>120</v>
+        <v>88</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H96" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H96" s="22">
+        <v>43472</v>
+      </c>
       <c r="I96" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J96" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="22"/>
-      <c r="L96" s="10"/>
+      <c r="K96" s="22">
+        <v>45140</v>
+      </c>
+      <c r="L96" s="31" t="s">
+        <v>485</v>
+      </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
       <c r="O96" s="10"/>
@@ -5456,26 +5691,32 @@
         <v>85</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="F97" s="31" t="s">
-        <v>120</v>
+        <v>90</v>
+      </c>
+      <c r="F97" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H97" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H97" s="22">
+        <v>43183</v>
+      </c>
       <c r="I97" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J97" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K97" s="22"/>
-      <c r="L97" s="10"/>
+      <c r="K97" s="22">
+        <v>45140</v>
+      </c>
+      <c r="L97" s="31" t="s">
+        <v>483</v>
+      </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10"/>
       <c r="O97" s="10"/>
@@ -5491,29 +5732,41 @@
         <v>102</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="F98" s="31" t="s">
-        <v>120</v>
+        <v>477</v>
+      </c>
+      <c r="F98" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H98" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H98" s="22">
+        <v>43302</v>
+      </c>
       <c r="I98" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J98" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K98" s="22"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
-      <c r="N98" s="10"/>
-      <c r="O98" s="10"/>
+      <c r="K98" s="22">
+        <v>45145</v>
+      </c>
+      <c r="L98" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="M98" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="N98" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="O98" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="99" spans="1:15">
       <c r="A99" s="10">
@@ -5526,16 +5779,16 @@
         <v>87</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="F99" s="31" t="s">
-        <v>120</v>
+        <v>78</v>
+      </c>
+      <c r="F99" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="H99" s="22"/>
       <c r="I99" s="14" t="s">
@@ -5561,26 +5814,32 @@
         <v>71</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="F100" s="31" t="s">
-        <v>120</v>
+        <v>94</v>
+      </c>
+      <c r="F100" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H100" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H100" s="22">
+        <v>43452</v>
+      </c>
       <c r="I100" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J100" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="22"/>
-      <c r="L100" s="10"/>
+      <c r="K100" s="22">
+        <v>45139</v>
+      </c>
+      <c r="L100" s="31" t="s">
+        <v>481</v>
+      </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
       <c r="O100" s="10"/>
@@ -5596,26 +5855,32 @@
         <v>81</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>107</v>
+        <v>488</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="F101" s="31" t="s">
-        <v>120</v>
+        <v>489</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H101" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H101" s="22">
+        <v>41946</v>
+      </c>
       <c r="I101" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J101" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="22"/>
-      <c r="L101" s="10"/>
+      <c r="K101" s="22">
+        <v>45139</v>
+      </c>
+      <c r="L101" s="31" t="s">
+        <v>490</v>
+      </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10"/>
       <c r="O101" s="10"/>
@@ -5631,26 +5896,32 @@
         <v>82</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="F102" s="31" t="s">
-        <v>120</v>
+        <v>96</v>
+      </c>
+      <c r="F102" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H102" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H102" s="22">
+        <v>43535</v>
+      </c>
       <c r="I102" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J102" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K102" s="22"/>
-      <c r="L102" s="10"/>
+      <c r="K102" s="22">
+        <v>45140</v>
+      </c>
+      <c r="L102" s="31" t="s">
+        <v>487</v>
+      </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10"/>
       <c r="O102" s="10"/>
@@ -5666,26 +5937,32 @@
         <v>68</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F103" s="31" t="s">
-        <v>120</v>
+        <v>98</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H103" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H103" s="22">
+        <v>43447</v>
+      </c>
       <c r="I103" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J103" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K103" s="22"/>
-      <c r="L103" s="10"/>
+      <c r="K103" s="22">
+        <v>45139</v>
+      </c>
+      <c r="L103" s="31" t="s">
+        <v>493</v>
+      </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10"/>
       <c r="O103" s="10"/>
@@ -5701,26 +5978,32 @@
         <v>69</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="F104" s="31" t="s">
-        <v>120</v>
+        <v>100</v>
+      </c>
+      <c r="F104" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H104" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H104" s="22">
+        <v>43436</v>
+      </c>
       <c r="I104" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J104" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K104" s="22"/>
-      <c r="L104" s="10"/>
+      <c r="K104" s="22">
+        <v>45139</v>
+      </c>
+      <c r="L104" s="31" t="s">
+        <v>492</v>
+      </c>
       <c r="M104" s="10"/>
       <c r="N104" s="10"/>
       <c r="O104" s="10"/>
@@ -5736,26 +6019,32 @@
         <v>70</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E105" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="F105" s="31" t="s">
-        <v>120</v>
+        <v>102</v>
+      </c>
+      <c r="F105" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H105" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H105" s="22">
+        <v>43498</v>
+      </c>
       <c r="I105" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J105" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K105" s="22"/>
-      <c r="L105" s="10"/>
+      <c r="K105" s="22">
+        <v>45139</v>
+      </c>
+      <c r="L105" s="31" t="s">
+        <v>491</v>
+      </c>
       <c r="M105" s="10"/>
       <c r="N105" s="10"/>
       <c r="O105" s="10"/>
@@ -5771,29 +6060,37 @@
         <v>103</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F106" s="31" t="s">
-        <v>120</v>
+        <v>76</v>
+      </c>
+      <c r="F106" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H106" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H106" s="22">
+        <v>43086</v>
+      </c>
       <c r="I106" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K106" s="22"/>
-      <c r="L106" s="10"/>
+      <c r="K106" s="22">
+        <v>45145</v>
+      </c>
+      <c r="L106" s="31" t="s">
+        <v>476</v>
+      </c>
       <c r="M106" s="10"/>
       <c r="N106" s="10"/>
-      <c r="O106" s="10"/>
+      <c r="O106" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="107" spans="1:15">
       <c r="A107" s="10">
@@ -5806,26 +6103,32 @@
         <v>149</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="F107" s="31" t="s">
-        <v>120</v>
+        <v>105</v>
+      </c>
+      <c r="F107" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="22"/>
+        <v>205</v>
+      </c>
+      <c r="H107" s="22">
+        <v>43462</v>
+      </c>
       <c r="I107" s="14" t="s">
         <v>15</v>
       </c>
       <c r="J107" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K107" s="22"/>
-      <c r="L107" s="10"/>
+      <c r="K107" s="22">
+        <v>45519</v>
+      </c>
+      <c r="L107" s="31" t="s">
+        <v>469</v>
+      </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10"/>
       <c r="O107" s="10"/>
@@ -5839,16 +6142,16 @@
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="8" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F108" s="31" t="s">
-        <v>74</v>
+        <v>108</v>
+      </c>
+      <c r="F108" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H108" s="22"/>
       <c r="I108" s="14" t="s">
@@ -5874,16 +6177,16 @@
       </c>
       <c r="C109" s="14"/>
       <c r="D109" s="8" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F109" s="31" t="s">
-        <v>74</v>
+        <v>109</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H109" s="22"/>
       <c r="I109" s="14" t="s">
@@ -5907,16 +6210,16 @@
       </c>
       <c r="C110" s="14"/>
       <c r="D110" s="8" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F110" s="31" t="s">
-        <v>74</v>
+        <v>111</v>
+      </c>
+      <c r="F110" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="14" t="s">
@@ -5940,16 +6243,16 @@
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="8" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="F111" s="31" t="s">
-        <v>74</v>
+        <v>382</v>
+      </c>
+      <c r="F111" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H111" s="22">
         <v>43102</v>
@@ -5977,16 +6280,16 @@
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="8" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F112" s="31" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="F112" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H112" s="22">
         <v>43368</v>
@@ -6001,13 +6304,15 @@
         <v>45208</v>
       </c>
       <c r="L112" s="10" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="N112" s="10"/>
-      <c r="O112" s="10"/>
+      <c r="O112" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="10">
@@ -6018,16 +6323,16 @@
       </c>
       <c r="C113" s="14"/>
       <c r="D113" s="8" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F113" s="31" t="s">
-        <v>74</v>
+        <v>114</v>
+      </c>
+      <c r="F113" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H113" s="22"/>
       <c r="I113" s="14" t="s">
@@ -6051,16 +6356,16 @@
       </c>
       <c r="C114" s="14"/>
       <c r="D114" s="8" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="F114" s="31" t="s">
-        <v>74</v>
+        <v>28</v>
+      </c>
+      <c r="F114" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H114" s="22">
         <v>42971</v>
@@ -6075,13 +6380,15 @@
         <v>45226</v>
       </c>
       <c r="L114" s="10" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="N114" s="10"/>
-      <c r="O114" s="10"/>
+      <c r="O114" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="10">
@@ -6092,16 +6399,16 @@
       </c>
       <c r="C115" s="14"/>
       <c r="D115" s="8" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="F115" s="31" t="s">
-        <v>74</v>
+        <v>116</v>
+      </c>
+      <c r="F115" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H115" s="22"/>
       <c r="I115" s="14" t="s">
@@ -6125,16 +6432,16 @@
       </c>
       <c r="C116" s="14"/>
       <c r="D116" s="8" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F116" s="31" t="s">
-        <v>74</v>
+        <v>118</v>
+      </c>
+      <c r="F116" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H116" s="22">
         <v>42950</v>
@@ -6149,7 +6456,7 @@
         <v>45206</v>
       </c>
       <c r="L116" s="10" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
@@ -6164,16 +6471,16 @@
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="8" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F117" s="31" t="s">
-        <v>74</v>
+        <v>119</v>
+      </c>
+      <c r="F117" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H117" s="22">
         <v>43321</v>
@@ -6188,10 +6495,10 @@
         <v>45201</v>
       </c>
       <c r="L117" s="10" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="N117" s="10"/>
       <c r="O117" s="10"/>
@@ -6205,16 +6512,16 @@
       </c>
       <c r="C118" s="14"/>
       <c r="D118" s="8" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="F118" s="31" t="s">
-        <v>74</v>
+        <v>121</v>
+      </c>
+      <c r="F118" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H118" s="22"/>
       <c r="I118" s="14" t="s">
@@ -6238,16 +6545,16 @@
       </c>
       <c r="C119" s="14"/>
       <c r="D119" s="8" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="F119" s="31" t="s">
-        <v>74</v>
+        <v>123</v>
+      </c>
+      <c r="F119" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H119" s="22"/>
       <c r="I119" s="14" t="s">
@@ -6271,16 +6578,16 @@
       </c>
       <c r="C120" s="14"/>
       <c r="D120" s="8" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F120" s="31" t="s">
-        <v>74</v>
+        <v>52</v>
+      </c>
+      <c r="F120" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H120" s="22"/>
       <c r="I120" s="14" t="s">
@@ -6304,16 +6611,16 @@
       </c>
       <c r="C121" s="14"/>
       <c r="D121" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F121" s="31" t="s">
-        <v>74</v>
+        <v>124</v>
+      </c>
+      <c r="F121" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H121" s="22"/>
       <c r="I121" s="14" t="s">
@@ -6337,16 +6644,16 @@
       </c>
       <c r="C122" s="14"/>
       <c r="D122" s="8" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="F122" s="31" t="s">
-        <v>74</v>
+        <v>126</v>
+      </c>
+      <c r="F122" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G122" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H122" s="22"/>
       <c r="I122" s="14" t="s">
@@ -6370,16 +6677,16 @@
       </c>
       <c r="C123" s="14"/>
       <c r="D123" s="8" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F123" s="31" t="s">
-        <v>74</v>
+        <v>128</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H123" s="22"/>
       <c r="I123" s="14" t="s">
@@ -6403,16 +6710,16 @@
       </c>
       <c r="C124" s="14"/>
       <c r="D124" s="8" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F124" s="31" t="s">
-        <v>74</v>
+        <v>130</v>
+      </c>
+      <c r="F124" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G124" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H124" s="22"/>
       <c r="I124" s="14" t="s">
@@ -6436,16 +6743,16 @@
       </c>
       <c r="C125" s="14"/>
       <c r="D125" s="8" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F125" s="31" t="s">
-        <v>74</v>
+        <v>124</v>
+      </c>
+      <c r="F125" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H125" s="22"/>
       <c r="I125" s="14" t="s">
@@ -6469,16 +6776,16 @@
       </c>
       <c r="C126" s="14"/>
       <c r="D126" s="8" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F126" s="31" t="s">
-        <v>74</v>
+        <v>133</v>
+      </c>
+      <c r="F126" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H126" s="22"/>
       <c r="I126" s="14" t="s">
@@ -6502,16 +6809,16 @@
       </c>
       <c r="C127" s="14"/>
       <c r="D127" s="8" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H127" s="22"/>
       <c r="I127" s="14" t="s">
@@ -6535,16 +6842,16 @@
       </c>
       <c r="C128" s="14"/>
       <c r="D128" s="8" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H128" s="22"/>
       <c r="I128" s="14" t="s">
@@ -6568,16 +6875,16 @@
       </c>
       <c r="C129" s="14"/>
       <c r="D129" s="8" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H129" s="22"/>
       <c r="I129" s="14" t="s">
@@ -6601,16 +6908,16 @@
       </c>
       <c r="C130" s="14"/>
       <c r="D130" s="8" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G130" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H130" s="22"/>
       <c r="I130" s="14" t="s">
@@ -6634,16 +6941,16 @@
       </c>
       <c r="C131" s="14"/>
       <c r="D131" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="E131" s="9" t="s">
-        <v>356</v>
+        <v>142</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>477</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H131" s="22">
         <v>42749</v>
@@ -6658,15 +6965,17 @@
         <v>45201</v>
       </c>
       <c r="L131" s="10" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="O131" s="10"/>
+        <v>369</v>
+      </c>
+      <c r="O131" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="132" spans="1:15">
       <c r="A132" s="10">
@@ -6677,16 +6986,16 @@
       </c>
       <c r="C132" s="14"/>
       <c r="D132" s="8" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H132" s="22"/>
       <c r="I132" s="14" t="s">
@@ -6710,16 +7019,16 @@
       </c>
       <c r="C133" s="14"/>
       <c r="D133" s="8" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H133" s="22">
         <v>42917</v>
@@ -6747,16 +7056,16 @@
       </c>
       <c r="C134" s="14"/>
       <c r="D134" s="8" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H134" s="22">
         <v>43372</v>
@@ -6784,16 +7093,16 @@
       </c>
       <c r="C135" s="14"/>
       <c r="D135" s="8" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H135" s="22"/>
       <c r="I135" s="14" t="s">
@@ -6817,16 +7126,16 @@
       </c>
       <c r="C136" s="14"/>
       <c r="D136" s="8" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H136" s="22"/>
       <c r="I136" s="14" t="s">
@@ -6850,16 +7159,16 @@
       </c>
       <c r="C137" s="14"/>
       <c r="D137" s="8" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H137" s="22">
         <v>46060</v>
@@ -6874,7 +7183,7 @@
         <v>45227</v>
       </c>
       <c r="L137" s="10" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="M137" s="10"/>
       <c r="N137" s="10"/>
@@ -6889,16 +7198,16 @@
       </c>
       <c r="C138" s="14"/>
       <c r="D138" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H138" s="22"/>
       <c r="I138" s="14" t="s">
@@ -6922,16 +7231,16 @@
       </c>
       <c r="C139" s="14"/>
       <c r="D139" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H139" s="22"/>
       <c r="I139" s="14" t="s">
@@ -6955,16 +7264,16 @@
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="5" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H140" s="22"/>
       <c r="I140" s="14" t="s">
@@ -6988,16 +7297,16 @@
       </c>
       <c r="C141" s="14"/>
       <c r="D141" s="8" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H141" s="22"/>
       <c r="I141" s="14" t="s">
@@ -7021,16 +7330,16 @@
       </c>
       <c r="C142" s="14"/>
       <c r="D142" s="8" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H142" s="22"/>
       <c r="I142" s="14" t="s">
@@ -7054,16 +7363,16 @@
       </c>
       <c r="C143" s="14"/>
       <c r="D143" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H143" s="22"/>
       <c r="I143" s="14" t="s">
@@ -7087,16 +7396,16 @@
       </c>
       <c r="C144" s="14"/>
       <c r="D144" s="8" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H144" s="22">
         <v>43258</v>
@@ -7124,16 +7433,16 @@
       </c>
       <c r="C145" s="14"/>
       <c r="D145" s="8" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H145" s="22"/>
       <c r="I145" s="14" t="s">
@@ -7157,16 +7466,16 @@
       </c>
       <c r="C146" s="14"/>
       <c r="D146" s="8" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H146" s="22"/>
       <c r="I146" s="14" t="s">
@@ -7190,16 +7499,16 @@
       </c>
       <c r="C147" s="14"/>
       <c r="D147" s="8" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H147" s="22"/>
       <c r="I147" s="14" t="s">
@@ -7223,16 +7532,16 @@
       </c>
       <c r="C148" s="14"/>
       <c r="D148" s="8" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H148" s="22"/>
       <c r="I148" s="14" t="s">
@@ -7256,16 +7565,16 @@
       </c>
       <c r="C149" s="21"/>
       <c r="D149" s="8" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H149" s="22"/>
       <c r="I149" s="14" t="s">
@@ -7289,16 +7598,16 @@
       </c>
       <c r="C150" s="21"/>
       <c r="D150" s="8" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H150" s="22"/>
       <c r="I150" s="14" t="s">
@@ -7322,16 +7631,16 @@
       </c>
       <c r="C151" s="21"/>
       <c r="D151" s="8" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H151" s="22">
         <v>42840</v>
@@ -7345,7 +7654,9 @@
       <c r="K151" s="22">
         <v>45206</v>
       </c>
-      <c r="L151" s="10"/>
+      <c r="L151" s="31" t="s">
+        <v>505</v>
+      </c>
       <c r="M151" s="10"/>
       <c r="N151" s="10"/>
       <c r="O151" s="10"/>
@@ -7359,16 +7670,16 @@
       </c>
       <c r="C152" s="21"/>
       <c r="D152" s="8" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H152" s="22">
         <v>43582</v>
@@ -7396,16 +7707,16 @@
       </c>
       <c r="C153" s="21"/>
       <c r="D153" s="8" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H153" s="22">
         <v>43071</v>
@@ -7418,7 +7729,7 @@
       </c>
       <c r="K153" s="22"/>
       <c r="L153" s="10" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="M153" s="10"/>
       <c r="N153" s="10"/>
@@ -7433,16 +7744,16 @@
       </c>
       <c r="C154" s="21"/>
       <c r="D154" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E154" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="E154" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="F154" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G154" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H154" s="22">
         <v>42752</v>
@@ -7455,7 +7766,7 @@
       </c>
       <c r="K154" s="22"/>
       <c r="L154" s="10" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="M154" s="10"/>
       <c r="N154" s="10"/>
@@ -7470,16 +7781,16 @@
       </c>
       <c r="C155" s="21"/>
       <c r="D155" s="8" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H155" s="22"/>
       <c r="I155" s="14" t="s">
@@ -7505,16 +7816,16 @@
         <v>130</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G156" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H156" s="22">
         <v>43046</v>
@@ -7529,12 +7840,12 @@
         <v>45231</v>
       </c>
       <c r="L156" s="10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="M156" s="10"/>
       <c r="N156" s="10"/>
       <c r="O156" s="10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="157" spans="1:15">
@@ -7548,16 +7859,16 @@
         <v>129</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H157" s="22">
         <v>43387</v>
@@ -7572,12 +7883,12 @@
         <v>45231</v>
       </c>
       <c r="L157" s="10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="M157" s="10"/>
       <c r="N157" s="10"/>
       <c r="O157" s="10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="158" spans="1:15">
@@ -7589,16 +7900,16 @@
       </c>
       <c r="C158" s="21"/>
       <c r="D158" s="8" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G158" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H158" s="22"/>
       <c r="I158" s="14" t="s">
@@ -7622,16 +7933,16 @@
       </c>
       <c r="C159" s="21"/>
       <c r="D159" s="8" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H159" s="22">
         <v>43211</v>
@@ -7646,11 +7957,13 @@
         <v>44774</v>
       </c>
       <c r="L159" s="10" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="M159" s="10"/>
       <c r="N159" s="10"/>
-      <c r="O159" s="10"/>
+      <c r="O159" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="160" spans="1:15">
       <c r="A160" s="10">
@@ -7661,16 +7974,16 @@
       </c>
       <c r="C160" s="21"/>
       <c r="D160" s="8" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G160" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H160" s="22">
         <v>42931</v>
@@ -7698,16 +8011,16 @@
       </c>
       <c r="C161" s="21"/>
       <c r="D161" s="8" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H161" s="22"/>
       <c r="I161" s="14" t="s">
@@ -7731,16 +8044,16 @@
       </c>
       <c r="C162" s="21"/>
       <c r="D162" s="8" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G162" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H162" s="22"/>
       <c r="I162" s="14" t="s">
@@ -7766,16 +8079,16 @@
         <v>33</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="H163" s="22">
         <v>43073</v>
@@ -7790,10 +8103,10 @@
         <v>44775</v>
       </c>
       <c r="L163" s="10" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="M163" s="10" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="N163" s="10"/>
       <c r="O163" s="10"/>
@@ -7807,16 +8120,16 @@
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="5" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G164" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H164" s="22"/>
       <c r="I164" s="14" t="s">
@@ -7840,16 +8153,16 @@
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="8" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H165" s="22"/>
       <c r="I165" s="14" t="s">
@@ -7873,16 +8186,16 @@
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="8" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G166" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H166" s="22"/>
       <c r="I166" s="14" t="s">
@@ -7906,16 +8219,16 @@
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="8" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H167" s="22"/>
       <c r="I167" s="14" t="s">
@@ -7939,16 +8252,16 @@
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="8" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E168" s="9" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G168" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H168" s="22"/>
       <c r="I168" s="14" t="s">
@@ -7972,16 +8285,16 @@
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="8" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H169" s="22"/>
       <c r="I169" s="14" t="s">
@@ -8005,16 +8318,16 @@
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="8" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G170" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H170" s="22"/>
       <c r="I170" s="14" t="s">
@@ -8038,16 +8351,16 @@
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="8" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H171" s="22"/>
       <c r="I171" s="14" t="s">
@@ -8071,16 +8384,16 @@
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="8" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G172" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H172" s="22"/>
       <c r="I172" s="14" t="s">
@@ -8104,16 +8417,16 @@
       </c>
       <c r="C173" s="19"/>
       <c r="D173" s="8" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H173" s="22">
         <v>43012</v>
@@ -8128,7 +8441,7 @@
         <v>44774</v>
       </c>
       <c r="L173" s="10" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="M173" s="10"/>
       <c r="N173" s="10"/>
@@ -8143,16 +8456,16 @@
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="8" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G174" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H174" s="22"/>
       <c r="I174" s="14" t="s">
@@ -8176,16 +8489,16 @@
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="8" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H175" s="22"/>
       <c r="I175" s="14" t="s">
@@ -8209,16 +8522,16 @@
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="8" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E176" s="9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F176" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G176" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H176" s="22"/>
       <c r="I176" s="14" t="s">
@@ -8242,16 +8555,16 @@
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="8" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="F177" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H177" s="22"/>
       <c r="I177" s="14" t="s">
@@ -8275,16 +8588,16 @@
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="8" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F178" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G178" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H178" s="22">
         <v>42349</v>
@@ -8299,11 +8612,13 @@
         <v>44776</v>
       </c>
       <c r="L178" s="10" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="M178" s="10"/>
       <c r="N178" s="10"/>
-      <c r="O178" s="10"/>
+      <c r="O178" s="31" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="10">
@@ -8314,16 +8629,16 @@
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="8" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H179" s="22"/>
       <c r="I179" s="14" t="s">
@@ -8347,16 +8662,16 @@
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="8" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="E180" s="9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G180" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H180" s="22"/>
       <c r="I180" s="14" t="s">
@@ -8380,16 +8695,16 @@
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="8" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F181" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H181" s="22"/>
       <c r="I181" s="14" t="s">
@@ -8413,16 +8728,16 @@
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="8" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E182" s="9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F182" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G182" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H182" s="22"/>
       <c r="I182" s="14" t="s">
@@ -8446,16 +8761,16 @@
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="8" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>27</v>
       </c>
       <c r="F183" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H183" s="22"/>
       <c r="I183" s="14" t="s">
@@ -8479,16 +8794,16 @@
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="8" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="E184" s="9" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G184" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H184" s="22"/>
       <c r="I184" s="14" t="s">
@@ -8512,16 +8827,16 @@
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="8" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H185" s="22"/>
       <c r="I185" s="14" t="s">
@@ -8545,16 +8860,16 @@
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="8" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E186" s="9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F186" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G186" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H186" s="22"/>
       <c r="I186" s="14" t="s">
@@ -8578,16 +8893,16 @@
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="8" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H187" s="22"/>
       <c r="I187" s="14" t="s">
@@ -8611,14 +8926,14 @@
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="8" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="E188" s="9"/>
       <c r="F188" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G188" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H188" s="22"/>
       <c r="I188" s="14" t="s">
@@ -8642,16 +8957,16 @@
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="8" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H189" s="22"/>
       <c r="I189" s="14" t="s">
@@ -8675,16 +8990,16 @@
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="8" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G190" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H190" s="22"/>
       <c r="I190" s="14" t="s">
@@ -8708,16 +9023,16 @@
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="8" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H191" s="22"/>
       <c r="I191" s="14" t="s">
@@ -8741,16 +9056,16 @@
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="8" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G192" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H192" s="22"/>
       <c r="I192" s="14" t="s">
@@ -8774,16 +9089,16 @@
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="8" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H193" s="22"/>
       <c r="I193" s="14" t="s">
@@ -8807,16 +9122,16 @@
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="8" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F194" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G194" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H194" s="22"/>
       <c r="I194" s="14" t="s">
@@ -8840,16 +9155,16 @@
       </c>
       <c r="C195" s="7"/>
       <c r="D195" s="8" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H195" s="22"/>
       <c r="I195" s="14" t="s">
@@ -8873,16 +9188,16 @@
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="8" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G196" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H196" s="22"/>
       <c r="I196" s="14" t="s">
@@ -8906,16 +9221,16 @@
       </c>
       <c r="C197" s="7"/>
       <c r="D197" s="8" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H197" s="22"/>
       <c r="I197" s="14" t="s">
@@ -8939,16 +9254,16 @@
       </c>
       <c r="C198" s="7"/>
       <c r="D198" s="8" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G198" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H198" s="22"/>
       <c r="I198" s="14" t="s">
@@ -8972,16 +9287,16 @@
       </c>
       <c r="C199" s="7"/>
       <c r="D199" s="8" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H199" s="22"/>
       <c r="I199" s="14" t="s">
@@ -9005,16 +9320,16 @@
       </c>
       <c r="C200" s="7"/>
       <c r="D200" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G200" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H200" s="22"/>
       <c r="I200" s="14" t="s">
@@ -9038,16 +9353,16 @@
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="8" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H201" s="22"/>
       <c r="I201" s="14" t="s">
@@ -9071,16 +9386,16 @@
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="8" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G202" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H202" s="22"/>
       <c r="I202" s="14" t="s">
@@ -9104,16 +9419,16 @@
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="8" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="F203" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H203" s="22"/>
       <c r="I203" s="14" t="s">
@@ -9137,16 +9452,16 @@
       </c>
       <c r="C204" s="7"/>
       <c r="D204" s="8" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>23</v>
       </c>
       <c r="F204" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G204" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H204" s="22"/>
       <c r="I204" s="14" t="s">
@@ -9170,16 +9485,16 @@
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="8" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F205" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H205" s="22"/>
       <c r="I205" s="14" t="s">
@@ -9203,16 +9518,16 @@
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="8" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F206" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G206" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H206" s="22"/>
       <c r="I206" s="14" t="s">
@@ -9236,16 +9551,16 @@
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="8" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="F207" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H207" s="22"/>
       <c r="I207" s="14" t="s">
@@ -9269,16 +9584,16 @@
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="8" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G208" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H208" s="22"/>
       <c r="I208" s="14" t="s">
@@ -9302,16 +9617,16 @@
       </c>
       <c r="C209" s="7"/>
       <c r="D209" s="8" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="F209" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H209" s="22"/>
       <c r="I209" s="14" t="s">
@@ -9335,16 +9650,16 @@
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="8" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="F210" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G210" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H210" s="22"/>
       <c r="I210" s="14" t="s">
@@ -9368,16 +9683,16 @@
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="8" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H211" s="22"/>
       <c r="I211" s="14" t="s">
@@ -9401,16 +9716,16 @@
       </c>
       <c r="C212" s="7"/>
       <c r="D212" s="8" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G212" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H212" s="22"/>
       <c r="I212" s="14" t="s">
@@ -9434,16 +9749,16 @@
       </c>
       <c r="C213" s="7"/>
       <c r="D213" s="8" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="F213" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H213" s="22"/>
       <c r="I213" s="14" t="s">
@@ -9467,16 +9782,16 @@
       </c>
       <c r="C214" s="7"/>
       <c r="D214" s="8" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G214" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="H214" s="22"/>
       <c r="I214" s="14" t="s">
@@ -9502,16 +9817,16 @@
         <v>490</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="F215" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H215" s="22"/>
       <c r="I215" s="14" t="s">
@@ -9537,16 +9852,16 @@
         <v>646</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="F216" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G216" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H216" s="22"/>
       <c r="I216" s="14" t="s">
@@ -9572,16 +9887,16 @@
         <v>690</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="F217" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H217" s="22"/>
       <c r="I217" s="14" t="s">
@@ -9607,16 +9922,16 @@
         <v>684</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="F218" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G218" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H218" s="22"/>
       <c r="I218" s="14" t="s">
@@ -9642,16 +9957,16 @@
         <v>551</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H219" s="22"/>
       <c r="I219" s="14" t="s">
@@ -9677,16 +9992,16 @@
         <v>647</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="F220" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G220" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H220" s="22"/>
       <c r="I220" s="14" t="s">
@@ -9712,16 +10027,16 @@
         <v>585</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="F221" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H221" s="22"/>
       <c r="I221" s="14" t="s">
@@ -9747,16 +10062,16 @@
         <v>579</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="F222" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G222" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H222" s="22"/>
       <c r="I222" s="14" t="s">
@@ -9782,16 +10097,16 @@
         <v>555</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F223" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H223" s="22"/>
       <c r="I223" s="14" t="s">
@@ -9817,16 +10132,16 @@
         <v>691</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G224" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H224" s="22"/>
       <c r="I224" s="14" t="s">
@@ -9852,16 +10167,16 @@
         <v>528</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H225" s="22"/>
       <c r="I225" s="14" t="s">
@@ -9887,16 +10202,16 @@
         <v>689</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G226" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H226" s="22"/>
       <c r="I226" s="14" t="s">
@@ -9922,16 +10237,16 @@
         <v>479</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H227" s="22"/>
       <c r="I227" s="14" t="s">
@@ -9957,16 +10272,16 @@
         <v>648</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G228" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H228" s="22"/>
       <c r="I228" s="14" t="s">
@@ -9992,16 +10307,16 @@
         <v>578</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H229" s="22"/>
       <c r="I229" s="14" t="s">
@@ -10027,16 +10342,16 @@
         <v>573</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="F230" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G230" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H230" s="22"/>
       <c r="I230" s="14" t="s">
@@ -10062,16 +10377,16 @@
         <v>587</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="F231" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H231" s="22"/>
       <c r="I231" s="14" t="s">
@@ -10097,16 +10412,16 @@
         <v>575</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F232" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G232" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H232" s="22"/>
       <c r="I232" s="14" t="s">
@@ -10132,16 +10447,16 @@
         <v>586</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="F233" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H233" s="22"/>
       <c r="I233" s="14" t="s">
@@ -10167,16 +10482,16 @@
         <v>583</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="E234" s="9" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="F234" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G234" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H234" s="22"/>
       <c r="I234" s="14" t="s">
@@ -10202,16 +10517,16 @@
         <v>580</v>
       </c>
       <c r="D235" s="8" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="F235" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H235" s="22"/>
       <c r="I235" s="14" t="s">
@@ -10237,16 +10552,16 @@
         <v>480</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E236" s="9" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F236" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G236" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H236" s="22"/>
       <c r="I236" s="14" t="s">
@@ -10272,16 +10587,16 @@
         <v>576</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E237" s="9" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F237" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H237" s="22"/>
       <c r="I237" s="14" t="s">
@@ -10307,16 +10622,16 @@
         <v>685</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="F238" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G238" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H238" s="22"/>
       <c r="I238" s="14" t="s">
@@ -10342,16 +10657,16 @@
         <v>688</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="F239" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G239" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H239" s="22"/>
       <c r="I239" s="14" t="s">
@@ -10377,16 +10692,16 @@
         <v>546</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="F240" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H240" s="22"/>
       <c r="I240" s="14" t="s">
@@ -10410,16 +10725,16 @@
       </c>
       <c r="C241" s="7"/>
       <c r="D241" s="8" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="F241" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G241" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H241" s="22"/>
       <c r="I241" s="14" t="s">
@@ -10443,16 +10758,16 @@
       </c>
       <c r="C242" s="7"/>
       <c r="D242" s="8" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="F242" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G242" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H242" s="22"/>
       <c r="I242" s="14" t="s">
@@ -10476,16 +10791,16 @@
       </c>
       <c r="C243" s="7"/>
       <c r="D243" s="8" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="F243" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G243" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H243" s="22"/>
       <c r="I243" s="14" t="s">
@@ -10511,16 +10826,16 @@
         <v>544</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="E244" s="9" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G244" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H244" s="22"/>
       <c r="I244" s="14" t="s">
@@ -10546,16 +10861,16 @@
         <v>780</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="E245" s="9" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="F245" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G245" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H245" s="22"/>
       <c r="I245" s="14" t="s">
@@ -10581,16 +10896,16 @@
         <v>569</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="E246" s="9" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="F246" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G246" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H246" s="22"/>
       <c r="I246" s="14" t="s">
@@ -10616,16 +10931,16 @@
         <v>582</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E247" s="9" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="F247" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H247" s="22"/>
       <c r="I247" s="14" t="s">
@@ -10651,16 +10966,16 @@
         <v>574</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="E248" s="9" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="F248" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G248" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H248" s="22"/>
       <c r="I248" s="14" t="s">
@@ -10686,16 +11001,16 @@
         <v>571</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="E249" s="9" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="F249" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G249" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H249" s="22"/>
       <c r="I249" s="14" t="s">
@@ -10721,16 +11036,16 @@
         <v>526</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="E250" s="9" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F250" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G250" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H250" s="22"/>
       <c r="I250" s="14" t="s">
@@ -10756,16 +11071,16 @@
         <v>537</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="E251" s="9" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="F251" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H251" s="22"/>
       <c r="I251" s="14" t="s">
@@ -10791,16 +11106,16 @@
         <v>584</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E252" s="9" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="F252" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G252" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H252" s="22"/>
       <c r="I252" s="14" t="s">
@@ -10826,16 +11141,16 @@
         <v>520</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E253" s="9" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="F253" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G253" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H253" s="22"/>
       <c r="I253" s="14" t="s">
@@ -10861,16 +11176,16 @@
         <v>570</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="E254" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F254" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G254" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H254" s="22"/>
       <c r="I254" s="14" t="s">
@@ -10896,16 +11211,16 @@
         <v>687</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="E255" s="9" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="F255" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G255" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H255" s="22"/>
       <c r="I255" s="14" t="s">
@@ -10931,16 +11246,16 @@
         <v>581</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="E256" s="9" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F256" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G256" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H256" s="22"/>
       <c r="I256" s="14" t="s">
@@ -10966,16 +11281,16 @@
         <v>588</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="E257" s="9" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="F257" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G257" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H257" s="22"/>
       <c r="I257" s="14" t="s">
@@ -11001,16 +11316,16 @@
         <v>686</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="E258" s="9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F258" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G258" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H258" s="22"/>
       <c r="I258" s="14" t="s">
@@ -11036,16 +11351,16 @@
         <v>525</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="E259" s="9" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="F259" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G259" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H259" s="22"/>
       <c r="I259" s="14" t="s">
@@ -11071,16 +11386,16 @@
         <v>577</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="E260" s="9" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="F260" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G260" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H260" s="22"/>
       <c r="I260" s="14" t="s">
@@ -11106,16 +11421,16 @@
         <v>589</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="E261" s="9" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="F261" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G261" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H261" s="22"/>
       <c r="I261" s="14" t="s">
@@ -11139,16 +11454,16 @@
       </c>
       <c r="C262" s="7"/>
       <c r="D262" s="8" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="E262" s="9" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="F262" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G262" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H262" s="22"/>
       <c r="I262" s="14" t="s">
@@ -11172,16 +11487,16 @@
       </c>
       <c r="C263" s="7"/>
       <c r="D263" s="8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E263" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F263" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G263" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H263" s="22"/>
       <c r="I263" s="14" t="s">
@@ -11205,16 +11520,16 @@
       </c>
       <c r="C264" s="7"/>
       <c r="D264" s="8" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="E264" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F264" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G264" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H264" s="22"/>
       <c r="I264" s="14" t="s">
@@ -11240,16 +11555,16 @@
         <v>572</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="E265" s="9" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="F265" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G265" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H265" s="22"/>
       <c r="I265" s="14" t="s">
@@ -11275,16 +11590,16 @@
         <v>649</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="E266" s="9" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="F266" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G266" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H266" s="22"/>
       <c r="I266" s="14" t="s">
@@ -11308,16 +11623,16 @@
       </c>
       <c r="C267" s="7"/>
       <c r="D267" s="8" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="E267" s="9" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="F267" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G267" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H267" s="22"/>
       <c r="I267" s="14" t="s">
@@ -11341,16 +11656,16 @@
       </c>
       <c r="C268" s="7"/>
       <c r="D268" s="8" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E268" s="9" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="F268" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G268" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H268" s="22"/>
       <c r="I268" s="14" t="s">
@@ -11374,16 +11689,16 @@
       </c>
       <c r="C269" s="7"/>
       <c r="D269" s="8" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="E269" s="9" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="F269" s="10" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G269" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H269" s="22"/>
       <c r="I269" s="14" t="s">
@@ -11402,23 +11717,26 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="C52:C83">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C84:C107">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C84:C107">
+  <conditionalFormatting sqref="C108:C139">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C108:C139">
+  <conditionalFormatting sqref="C140:C163">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C140:C163">
+  <conditionalFormatting sqref="C215:C243">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C215:C243">
+  <conditionalFormatting sqref="C244:C269">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C244:C269">
+  <conditionalFormatting sqref="L1:L1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
@@ -11427,7 +11745,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231437DD-A302-428C-BE63-55EB2CC933D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -11438,34 +11756,34 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1"/>
     <row r="2" spans="1:2" s="20" customFormat="1" ht="21">
-      <c r="A2" s="26" t="s">
-        <v>402</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="B2" s="25">
         <f>COUNTIF('All Record'!$F$2:$F$1048576,"Female")</f>
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21">
-      <c r="A3" s="26" t="s">
-        <v>403</v>
-      </c>
-      <c r="B3" s="26">
+      <c r="A3" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="B3" s="25">
         <f>COUNTIF('All Record'!$F$52:$F$1048576,"Male")</f>
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21">
-      <c r="A4" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="B4" s="26">
+      <c r="A4" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="25">
         <f>B2+B3</f>
         <v>242</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
